--- a/artfynd/A 9567-2026 artfynd.xlsx
+++ b/artfynd/A 9567-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131914216</v>
       </c>
       <c r="B2" t="n">
-        <v>4774</v>
+        <v>4775</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>131914290</v>
       </c>
       <c r="B3" t="n">
-        <v>91838</v>
+        <v>91841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9567-2026 artfynd.xlsx
+++ b/artfynd/A 9567-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131914290</v>
       </c>
       <c r="B3" t="n">
-        <v>91841</v>
+        <v>91846</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9567-2026 artfynd.xlsx
+++ b/artfynd/A 9567-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131914290</v>
       </c>
       <c r="B3" t="n">
-        <v>91846</v>
+        <v>91848</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9567-2026 artfynd.xlsx
+++ b/artfynd/A 9567-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131914290</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9567-2026 artfynd.xlsx
+++ b/artfynd/A 9567-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131914290</v>
       </c>
       <c r="B3" t="n">
-        <v>91892</v>
+        <v>91898</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 9567-2026 artfynd.xlsx
+++ b/artfynd/A 9567-2026 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>131914290</v>
       </c>
       <c r="B3" t="n">
-        <v>91898</v>
+        <v>91908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
